--- a/data/trans_camb/P6903-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 15,45</t>
+          <t>-30,57; 10,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 22,36</t>
+          <t>-18,46; 24,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,12; 2,87</t>
+          <t>-43,75; 2,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 45,0</t>
+          <t>-6,1; 45,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 33,4</t>
+          <t>-14,9; 34,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 18,68</t>
+          <t>-35,06; 19,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 19,68</t>
+          <t>-14,43; 19,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 20,76</t>
+          <t>-12,99; 19,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 1,8</t>
+          <t>-33,82; 2,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 60,46</t>
+          <t>-63,32; 36,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 86,01</t>
+          <t>-35,91; 93,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,45; 14,19</t>
+          <t>-88,1; 15,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 190,77</t>
+          <t>-12,66; 191,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 153,64</t>
+          <t>-27,13; 151,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 83,08</t>
+          <t>-70,88; 90,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 63,73</t>
+          <t>-30,5; 65,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 66,77</t>
+          <t>-27,64; 64,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 8,65</t>
+          <t>-74,1; 11,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 18,44</t>
+          <t>-15,38; 18,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 25,78</t>
+          <t>-4,86; 26,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 33,13</t>
+          <t>-9,52; 35,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 14,73</t>
+          <t>-27,31; 17,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 51,91</t>
+          <t>6,91; 50,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 35,22</t>
+          <t>-4,57; 34,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 14,34</t>
+          <t>-14,58; 12,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 31,19</t>
+          <t>3,53; 31,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 27,83</t>
+          <t>-2,36; 28,94</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 85,02</t>
+          <t>-40,05; 96,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 137,52</t>
+          <t>-13,0; 116,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 149,36</t>
+          <t>-31,53; 159,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,33; 87,09</t>
+          <t>-71,15; 106,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,34; 326,4</t>
+          <t>15,87; 271,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 227,09</t>
+          <t>-12,92; 188,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 61,08</t>
+          <t>-41,28; 48,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 133,31</t>
+          <t>7,83; 133,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 124,76</t>
+          <t>-7,89; 122,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,62; -0,27</t>
+          <t>-40,51; 2,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 12,55</t>
+          <t>-36,24; 11,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,94; -6,49</t>
+          <t>-42,88; -5,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 40,82</t>
+          <t>-12,64; 40,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 28,77</t>
+          <t>-18,46; 26,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 29,6</t>
+          <t>-9,37; 28,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 10,86</t>
+          <t>-23,85; 11,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 9,15</t>
+          <t>-25,23; 11,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 5,23</t>
+          <t>-24,21; 3,86</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 9,37</t>
+          <t>-89,47; 21,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 65,52</t>
+          <t>-84,46; 63,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,08; -23,07</t>
+          <t>-89,62; -10,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 1148,58</t>
+          <t>-69,31; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 765,61</t>
+          <t>-39,96; 619,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,51; 69,85</t>
+          <t>-67,31; 66,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,22; 49,64</t>
+          <t>-74,48; 70,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 30,85</t>
+          <t>-62,55; 23,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 25,44</t>
+          <t>-9,52; 26,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 50,19</t>
+          <t>8,24; 49,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,04; 52,77</t>
+          <t>7,75; 54,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 54,09</t>
+          <t>4,85; 51,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 57,27</t>
+          <t>9,05; 55,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 56,18</t>
+          <t>-15,61; 56,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 30,28</t>
+          <t>2,46; 30,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,13; 46,45</t>
+          <t>15,34; 47,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 45,91</t>
+          <t>-5,76; 43,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 218,86</t>
+          <t>-40,63; 204,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,58; 404,54</t>
+          <t>21,19; 426,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,46; 450,78</t>
+          <t>23,1; 459,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,76; 1204,0</t>
+          <t>-1,84; 1164,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,59; 1309,18</t>
+          <t>13,08; 1242,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 792,86</t>
+          <t>-45,24; 946,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 248,73</t>
+          <t>7,2; 254,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,21; 382,48</t>
+          <t>63,55; 461,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 335,71</t>
+          <t>-12,43; 318,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-47,86; -4,15</t>
+          <t>-48,06; -3,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 51,13</t>
+          <t>-14,63; 54,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-39,43; 7,43</t>
+          <t>-40,91; 5,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 43,03</t>
+          <t>-44,99; 46,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 69,96</t>
+          <t>-35,74; 71,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 31,59</t>
+          <t>-43,54; 30,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 8,61</t>
+          <t>-35,01; 10,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 50,27</t>
+          <t>-9,38; 50,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 8,99</t>
+          <t>-31,96; 8,04</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,8</t>
+          <t>-100,0; 65,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 279,11</t>
+          <t>-37,41; 278,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,09; 83,61</t>
+          <t>-91,03; 47,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,81; —</t>
+          <t>-85,03; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,59; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,61; —</t>
+          <t>-79,54; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 52,14</t>
+          <t>-80,67; 68,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 279,49</t>
+          <t>-22,69; 270,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-70,82; 58,34</t>
+          <t>-73,41; 49,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-45,22; -4,98</t>
+          <t>-42,62; -4,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 26,85</t>
+          <t>-27,42; 25,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 3,22</t>
+          <t>-37,34; 4,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 47,14</t>
+          <t>-3,07; 46,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,89; 80,78</t>
+          <t>0,35; 78,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 35,22</t>
+          <t>-4,92; 35,52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 3,55</t>
+          <t>-29,51; 3,5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 31,94</t>
+          <t>-13,37; 32,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 8,1</t>
+          <t>-23,38; 9,0</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,62; -10,04</t>
+          <t>-81,89; -2,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 85,44</t>
+          <t>-52,02; 80,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 15,57</t>
+          <t>-71,91; 20,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-71,12; 16,04</t>
+          <t>-70,44; 18,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 137,34</t>
+          <t>-35,72; 137,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 32,92</t>
+          <t>-55,32; 40,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 1,9</t>
+          <t>-26,47; 0,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 18,27</t>
+          <t>-11,53; 19,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 8,39</t>
+          <t>-19,58; 8,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 14,59</t>
+          <t>-23,24; 14,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 20,06</t>
+          <t>-17,75; 21,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 24,76</t>
+          <t>-8,05; 25,72</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 4,36</t>
+          <t>-19,8; 2,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 14,33</t>
+          <t>-9,06; 14,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 11,75</t>
+          <t>-8,63; 12,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-77,1; 15,4</t>
+          <t>-76,8; 6,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 90,41</t>
+          <t>-32,8; 93,55</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 41,72</t>
+          <t>-57,19; 39,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 75,83</t>
+          <t>-58,28; 78,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,89; 104,53</t>
+          <t>-44,65; 120,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 125,95</t>
+          <t>-19,23; 133,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 20,97</t>
+          <t>-58,63; 9,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 64,54</t>
+          <t>-26,59; 61,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 49,58</t>
+          <t>-26,21; 58,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 16,79</t>
+          <t>-17,1; 17,17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 20,23</t>
+          <t>-14,59; 19,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>19,19; 51,56</t>
+          <t>21,95; 51,12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 10,39</t>
+          <t>-38,47; 13,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-52,58; -6,61</t>
+          <t>-52,95; -8,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 30,06</t>
+          <t>-9,21; 29,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 11,17</t>
+          <t>-18,32; 8,57</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 5,12</t>
+          <t>-22,45; 6,2</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14,09; 38,2</t>
+          <t>14,94; 39,64</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 61,85</t>
+          <t>-46,16; 66,08</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 73,63</t>
+          <t>-40,21; 71,59</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50,87; 190,27</t>
+          <t>55,73; 194,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,24; 27,46</t>
+          <t>-67,55; 31,15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-92,45; -2,93</t>
+          <t>-91,82; -14,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 90,15</t>
+          <t>-15,5; 81,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 34,46</t>
+          <t>-44,27; 26,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-54,97; 15,07</t>
+          <t>-53,55; 17,95</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>30,73; 117,85</t>
+          <t>34,15; 123,53</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -1,34</t>
+          <t>-13,82; -0,63</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,2; 14,16</t>
+          <t>0,34; 14,16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 10,38</t>
+          <t>-4,45; 9,63</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,8</t>
+          <t>-5,52; 13,35</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,88</t>
+          <t>1,41; 20,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 17,25</t>
+          <t>-3,79; 16,95</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,88</t>
+          <t>-8,41; 2,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,26</t>
+          <t>3,3; 14,52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,88</t>
+          <t>-2,01; 10,84</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -4,91</t>
+          <t>-40,49; -2,09</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,38; 50,01</t>
+          <t>1,02; 49,35</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 35,78</t>
+          <t>-13,54; 33,1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 48,02</t>
+          <t>-15,07; 52,06</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,26; 78,9</t>
+          <t>4,13; 78,2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 64,66</t>
+          <t>-9,18; 62,47</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 6,57</t>
+          <t>-25,2; 8,32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9,51; 50,71</t>
+          <t>9,69; 49,85</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 36,91</t>
+          <t>-5,73; 37,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6903-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-20,99</t>
+          <t>-25,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,29</t>
+          <t>-13,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-17,15</t>
+          <t>-20,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 10,54</t>
+          <t>-30,92; 13,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 24,1</t>
+          <t>-20,7; 23,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 2,44</t>
+          <t>-45,2; -4,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 45,66</t>
+          <t>-8,39; 45,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 34,0</t>
+          <t>-12,68; 36,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 19,09</t>
+          <t>-37,82; 13,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 19,8</t>
+          <t>-13,66; 21,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 19,54</t>
+          <t>-10,19; 22,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 2,57</t>
+          <t>-35,55; -4,17</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-52,37%</t>
+          <t>-63,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-29,07%</t>
+          <t>-34,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-43,32%</t>
+          <t>-52,55%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 36,58</t>
+          <t>-64,41; 53,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 93,52</t>
+          <t>-40,18; 92,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,1; 15,51</t>
+          <t>-90,21; -2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 191,06</t>
+          <t>-18,1; 195,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 151,9</t>
+          <t>-26,38; 155,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 90,51</t>
+          <t>-76,8; 64,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 65,0</t>
+          <t>-29,76; 75,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 64,23</t>
+          <t>-21,49; 73,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 11,0</t>
+          <t>-76,55; -8,69</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,62</t>
+          <t>11,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,94</t>
+          <t>16,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,65</t>
+          <t>13,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 18,83</t>
+          <t>-14,88; 18,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 26,11</t>
+          <t>-6,09; 25,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 35,09</t>
+          <t>-7,96; 33,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 17,51</t>
+          <t>-27,51; 14,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 50,65</t>
+          <t>7,33; 53,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 34,22</t>
+          <t>-4,76; 37,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 12,04</t>
+          <t>-14,66; 11,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 31,13</t>
+          <t>4,94; 30,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 28,94</t>
+          <t>-0,05; 28,77</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 96,99</t>
+          <t>-39,72; 92,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 116,78</t>
+          <t>-18,26; 115,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 159,18</t>
+          <t>-23,23; 156,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,15; 106,2</t>
+          <t>-71,62; 91,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 271,04</t>
+          <t>14,1; 286,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 188,69</t>
+          <t>-11,75; 219,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 48,73</t>
+          <t>-40,0; 47,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 133,43</t>
+          <t>11,82; 133,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 122,03</t>
+          <t>1,04; 124,55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-24,02</t>
+          <t>-24,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>13,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,18</t>
+          <t>-8,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 2,46</t>
+          <t>-40,05; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 11,35</t>
+          <t>-36,41; 12,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,88; -5,73</t>
+          <t>-43,0; -5,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 40,28</t>
+          <t>-8,56; 41,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 26,44</t>
+          <t>-22,54; 24,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 28,63</t>
+          <t>-8,32; 27,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 11,08</t>
+          <t>-22,71; 11,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 11,63</t>
+          <t>-24,63; 12,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 3,86</t>
+          <t>-23,83; 3,09</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-69,73%</t>
+          <t>-70,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-30,66%</t>
+          <t>-31,05%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,47; 21,8</t>
+          <t>-88,79; 37,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,46; 63,54</t>
+          <t>-80,77; 50,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,62; -10,49</t>
+          <t>-89,4; -19,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,31; —</t>
+          <t>-54,87; 1075,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 619,54</t>
+          <t>-33,03; 631,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 66,62</t>
+          <t>-66,52; 76,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,48; 70,05</t>
+          <t>-71,61; 89,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,55; 23,66</t>
+          <t>-63,08; 20,28</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,02</t>
+          <t>35,44</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,51</t>
+          <t>48,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23,57</t>
+          <t>40,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 26,88</t>
+          <t>-9,23; 26,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 49,79</t>
+          <t>9,02; 51,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,75; 54,18</t>
+          <t>13,2; 57,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 51,7</t>
+          <t>4,89; 52,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,05; 55,65</t>
+          <t>11,27; 56,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 56,58</t>
+          <t>26,73; 64,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 30,35</t>
+          <t>2,06; 31,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,34; 47,24</t>
+          <t>15,06; 46,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 43,39</t>
+          <t>26,26; 53,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156,57%</t>
+          <t>178,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>174,11%</t>
+          <t>358,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130,65%</t>
+          <t>224,37%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 204,73</t>
+          <t>-39,58; 200,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,19; 426,33</t>
+          <t>25,22; 416,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,1; 459,85</t>
+          <t>44,78; 484,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1164,45</t>
+          <t>1,18; 1166,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,08; 1242,75</t>
+          <t>22,51; 1292,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 946,63</t>
+          <t>76,63; 1524,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2; 254,51</t>
+          <t>7,78; 304,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>63,55; 461,01</t>
+          <t>62,65; 432,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 318,15</t>
+          <t>98,19; 484,84</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-16,54</t>
+          <t>-17,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-11,41</t>
+          <t>-11,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-48,06; -3,78</t>
+          <t>-45,81; -2,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 54,39</t>
+          <t>-13,1; 56,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 5,74</t>
+          <t>-43,25; 5,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 46,65</t>
+          <t>-46,81; 46,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 71,17</t>
+          <t>-26,35; 71,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 30,77</t>
+          <t>-45,78; 27,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 10,5</t>
+          <t>-35,05; 9,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 50,24</t>
+          <t>-7,34; 50,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 8,04</t>
+          <t>-34,19; 7,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-52,24%</t>
+          <t>-56,61%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-8,03%</t>
+          <t>-5,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,75%</t>
+          <t>-38,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 65,9</t>
+          <t>-100,0; 142,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 278,0</t>
+          <t>-29,91; 324,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-91,03; 47,82</t>
+          <t>-90,37; 56,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-85,03; —</t>
+          <t>-83,07; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,77; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,54; —</t>
+          <t>-75,36; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 68,11</t>
+          <t>-83,32; 66,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 270,69</t>
+          <t>-21,16; 236,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 49,58</t>
+          <t>-73,2; 51,63</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-17,09</t>
+          <t>-16,55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>21,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>-6,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-42,62; -4,98</t>
+          <t>-44,09; -3,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 25,45</t>
+          <t>-25,29; 27,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 4,25</t>
+          <t>-37,42; 4,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 46,24</t>
+          <t>-7,68; 47,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,35; 78,29</t>
+          <t>0,48; 80,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 35,52</t>
+          <t>-2,52; 36,52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 3,5</t>
+          <t>-29,11; 3,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 32,94</t>
+          <t>-14,02; 30,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 9,0</t>
+          <t>-22,98; 9,91</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-40,41%</t>
+          <t>-39,14%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>279,07%</t>
+          <t>292,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-20,87%</t>
+          <t>-18,66%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-81,89; -2,87</t>
+          <t>-83,16; -6,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 80,14</t>
+          <t>-51,77; 87,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 20,24</t>
+          <t>-73,07; 16,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-70,44; 18,36</t>
+          <t>-70,48; 15,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,72; 137,46</t>
+          <t>-32,31; 129,99</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,32; 40,36</t>
+          <t>-51,76; 46,69</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>9,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>3,02</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 0,07</t>
+          <t>-26,73; 1,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 19,34</t>
+          <t>-11,25; 18,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 8,22</t>
+          <t>-18,49; 10,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 14,29</t>
+          <t>-24,36; 14,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 21,68</t>
+          <t>-19,35; 19,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 25,72</t>
+          <t>-5,91; 26,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 2,25</t>
+          <t>-20,41; 2,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 14,64</t>
+          <t>-9,21; 14,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 12,65</t>
+          <t>-8,55; 13,59</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-23,52%</t>
+          <t>-13,96%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 6,7</t>
+          <t>-76,53; 12,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 93,55</t>
+          <t>-32,85; 93,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 39,02</t>
+          <t>-56,08; 47,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 78,95</t>
+          <t>-61,15; 77,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 120,91</t>
+          <t>-45,68; 100,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 133,63</t>
+          <t>-14,75; 150,22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-58,63; 9,38</t>
+          <t>-59,76; 11,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 61,2</t>
+          <t>-25,88; 66,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 58,31</t>
+          <t>-24,01; 60,14</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37,5</t>
+          <t>37,35</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26,82</t>
+          <t>24,9</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 17,17</t>
+          <t>-16,32; 17,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 19,58</t>
+          <t>-15,76; 20,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>21,95; 51,12</t>
+          <t>22,26; 50,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 13,2</t>
+          <t>-36,62; 9,66</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-52,95; -8,51</t>
+          <t>-51,06; -6,25</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 29,17</t>
+          <t>-14,27; 23,53</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 8,57</t>
+          <t>-19,04; 8,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 6,2</t>
+          <t>-22,18; 4,13</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14,94; 39,64</t>
+          <t>12,87; 35,73</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113,28%</t>
+          <t>112,81%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 66,08</t>
+          <t>-43,47; 68,4</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 71,59</t>
+          <t>-42,41; 73,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>55,73; 194,13</t>
+          <t>57,53; 194,41</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 31,15</t>
+          <t>-65,07; 27,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-91,82; -14,12</t>
+          <t>-91,76; -10,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 81,62</t>
+          <t>-23,99; 62,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 26,68</t>
+          <t>-45,45; 25,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 17,95</t>
+          <t>-53,79; 13,26</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34,15; 123,53</t>
+          <t>27,86; 111,17</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>11,88</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>7,84</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-13,82; -0,63</t>
+          <t>-14,03; -1,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,34; 14,16</t>
+          <t>-0,54; 14,48</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 9,63</t>
+          <t>-2,31; 11,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 13,35</t>
+          <t>-5,18; 13,04</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,41; 20,43</t>
+          <t>2,29; 20,53</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 16,95</t>
+          <t>3,75; 19,09</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,44</t>
+          <t>-8,02; 2,76</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,3; 14,52</t>
+          <t>2,87; 14,49</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,84</t>
+          <t>2,59; 12,66</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -2,09</t>
+          <t>-41,26; -4,26</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1,02; 49,35</t>
+          <t>-0,78; 51,56</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 33,1</t>
+          <t>-7,2; 43,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 52,06</t>
+          <t>-14,61; 51,28</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,13; 78,2</t>
+          <t>5,88; 78,05</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 62,47</t>
+          <t>10,53; 72,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 8,32</t>
+          <t>-24,26; 10,46</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>9,69; 49,85</t>
+          <t>7,59; 49,2</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 37,27</t>
+          <t>7,64; 44,38</t>
         </is>
       </c>
     </row>
